--- a/WS_Boards.xlsx
+++ b/WS_Boards.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CCE8A7-AD9E-4009-94D6-CC12FC8D69BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="4188" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="4188" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Boards Catalogue" sheetId="4" r:id="rId1"/>
